--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124655748</v>
+        <v>124655288</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631831</v>
+        <v>631978</v>
       </c>
       <c r="R2" t="n">
-        <v>6899048</v>
+        <v>6899040</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124657511</v>
+        <v>124658065</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631929</v>
+        <v>631895</v>
       </c>
       <c r="R3" t="n">
-        <v>6899210</v>
+        <v>6899098</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1026,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658065</v>
+        <v>124659053</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>95551</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1033,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631895</v>
+        <v>631932</v>
       </c>
       <c r="R5" t="n">
-        <v>6899098</v>
+        <v>6898972</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,6 +1131,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1138,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124659053</v>
+        <v>124658193</v>
       </c>
       <c r="B6" t="n">
-        <v>95551</v>
+        <v>79795</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,43 +1183,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631932</v>
+        <v>631827</v>
       </c>
       <c r="R6" t="n">
-        <v>6898972</v>
+        <v>6899028</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,26 +1263,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1284,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124657989</v>
+        <v>124655597</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>95335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,34 +1295,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631885</v>
+        <v>631884</v>
       </c>
       <c r="R7" t="n">
-        <v>6899120</v>
+        <v>6899003</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1359,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124655288</v>
+        <v>124657989</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,25 +1412,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1436,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631978</v>
+        <v>631885</v>
       </c>
       <c r="R8" t="n">
-        <v>6899040</v>
+        <v>6899120</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124658193</v>
+        <v>124658225</v>
       </c>
       <c r="B9" t="n">
-        <v>79795</v>
+        <v>98135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,21 +1528,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631827</v>
+        <v>631825</v>
       </c>
       <c r="R9" t="n">
-        <v>6899028</v>
+        <v>6899023</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1620,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124658225</v>
+        <v>124655748</v>
       </c>
       <c r="B10" t="n">
-        <v>98135</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,21 +1640,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1660,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631825</v>
+        <v>631831</v>
       </c>
       <c r="R10" t="n">
-        <v>6899023</v>
+        <v>6899048</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1695,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124655597</v>
+        <v>124657511</v>
       </c>
       <c r="B11" t="n">
-        <v>95335</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,47 +1748,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631884</v>
+        <v>631929</v>
       </c>
       <c r="R11" t="n">
-        <v>6899003</v>
+        <v>6899210</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1816,7 +1811,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1821,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124655288</v>
+        <v>124658065</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631978</v>
+        <v>631895</v>
       </c>
       <c r="R2" t="n">
-        <v>6899040</v>
+        <v>6899098</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658065</v>
+        <v>124659053</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>95551</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631895</v>
+        <v>631932</v>
       </c>
       <c r="R3" t="n">
-        <v>6899098</v>
+        <v>6898972</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +897,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655624</v>
+        <v>124657989</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,51 +945,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631876</v>
+        <v>631885</v>
       </c>
       <c r="R4" t="n">
-        <v>6898985</v>
+        <v>6899120</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124659053</v>
+        <v>124657511</v>
       </c>
       <c r="B5" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,47 +1057,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631932</v>
+        <v>631929</v>
       </c>
       <c r="R5" t="n">
-        <v>6898972</v>
+        <v>6899210</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På murken granstubbe</t>
+          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,26 +1146,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1167,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658193</v>
+        <v>124655288</v>
       </c>
       <c r="B6" t="n">
-        <v>79795</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,38 +1174,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631827</v>
+        <v>631978</v>
       </c>
       <c r="R6" t="n">
-        <v>6899028</v>
+        <v>6899040</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124655597</v>
+        <v>124658193</v>
       </c>
       <c r="B7" t="n">
-        <v>95335</v>
+        <v>79795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,43 +1290,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631884</v>
+        <v>631827</v>
       </c>
       <c r="R7" t="n">
-        <v>6899003</v>
+        <v>6899028</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1363,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124657989</v>
+        <v>124655597</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>95335</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,34 +1402,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631885</v>
+        <v>631884</v>
       </c>
       <c r="R8" t="n">
-        <v>6899120</v>
+        <v>6899003</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1624,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124655748</v>
+        <v>124655624</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,41 +1631,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631831</v>
+        <v>631876</v>
       </c>
       <c r="R10" t="n">
-        <v>6899048</v>
+        <v>6898985</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1699,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124657511</v>
+        <v>124655748</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,38 +1753,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631929</v>
+        <v>631831</v>
       </c>
       <c r="R11" t="n">
-        <v>6899210</v>
+        <v>6899048</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1811,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1821,12 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658065</v>
+        <v>124655748</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631895</v>
+        <v>631831</v>
       </c>
       <c r="R2" t="n">
-        <v>6899098</v>
+        <v>6899048</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124659053</v>
+        <v>124657511</v>
       </c>
       <c r="B3" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631932</v>
+        <v>631929</v>
       </c>
       <c r="R3" t="n">
-        <v>6898972</v>
+        <v>6899210</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På murken granstubbe</t>
+          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,26 +888,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -933,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124657989</v>
+        <v>124658065</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -973,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631885</v>
+        <v>631895</v>
       </c>
       <c r="R4" t="n">
-        <v>6899120</v>
+        <v>6899098</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124657511</v>
+        <v>124658225</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>98135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,38 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631929</v>
+        <v>631825</v>
       </c>
       <c r="R5" t="n">
-        <v>6899210</v>
+        <v>6899023</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124655288</v>
+        <v>124659053</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>95551</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,38 +1140,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631978</v>
+        <v>631932</v>
       </c>
       <c r="R6" t="n">
-        <v>6899040</v>
+        <v>6898972</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1237,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1222,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,6 +1238,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1274,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658193</v>
+        <v>124655597</v>
       </c>
       <c r="B7" t="n">
-        <v>79795</v>
+        <v>95335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,34 +1290,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631827</v>
+        <v>631884</v>
       </c>
       <c r="R7" t="n">
-        <v>6899028</v>
+        <v>6899003</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1349,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124655597</v>
+        <v>124655288</v>
       </c>
       <c r="B8" t="n">
-        <v>95335</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,47 +1407,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631884</v>
+        <v>631978</v>
       </c>
       <c r="R8" t="n">
-        <v>6899003</v>
+        <v>6899040</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124658225</v>
+        <v>124655624</v>
       </c>
       <c r="B9" t="n">
-        <v>98135</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,41 +1519,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631825</v>
+        <v>631876</v>
       </c>
       <c r="R9" t="n">
-        <v>6899023</v>
+        <v>6898985</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124655624</v>
+        <v>124657989</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,51 +1641,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631876</v>
+        <v>631885</v>
       </c>
       <c r="R10" t="n">
-        <v>6898985</v>
+        <v>6899120</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124655748</v>
+        <v>124658193</v>
       </c>
       <c r="B11" t="n">
-        <v>91023</v>
+        <v>79795</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,21 +1757,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631831</v>
+        <v>631827</v>
       </c>
       <c r="R11" t="n">
-        <v>6899048</v>
+        <v>6899028</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124655748</v>
+        <v>124658225</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>98135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631831</v>
+        <v>631825</v>
       </c>
       <c r="R2" t="n">
-        <v>6899048</v>
+        <v>6899023</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124657511</v>
+        <v>124655288</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631929</v>
+        <v>631978</v>
       </c>
       <c r="R3" t="n">
-        <v>6899210</v>
+        <v>6899040</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658065</v>
+        <v>124655624</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +915,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631895</v>
+        <v>631876</v>
       </c>
       <c r="R4" t="n">
-        <v>6899098</v>
+        <v>6898985</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658225</v>
+        <v>124657511</v>
       </c>
       <c r="B5" t="n">
-        <v>98135</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1033,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631825</v>
+        <v>631929</v>
       </c>
       <c r="R5" t="n">
-        <v>6899023</v>
+        <v>6899210</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1274,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124655597</v>
+        <v>124658193</v>
       </c>
       <c r="B7" t="n">
-        <v>95335</v>
+        <v>79795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,43 +1300,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631884</v>
+        <v>631827</v>
       </c>
       <c r="R7" t="n">
-        <v>6899003</v>
+        <v>6899028</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1358,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124655288</v>
+        <v>124658065</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1412,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631978</v>
+        <v>631895</v>
       </c>
       <c r="R8" t="n">
-        <v>6899040</v>
+        <v>6899098</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124655624</v>
+        <v>124655748</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,51 +1520,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631876</v>
+        <v>631831</v>
       </c>
       <c r="R9" t="n">
-        <v>6898985</v>
+        <v>6899048</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1741,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124658193</v>
+        <v>124655597</v>
       </c>
       <c r="B11" t="n">
-        <v>79795</v>
+        <v>95335</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,34 +1748,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631827</v>
+        <v>631884</v>
       </c>
       <c r="R11" t="n">
-        <v>6899028</v>
+        <v>6899003</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658225</v>
+        <v>124655624</v>
       </c>
       <c r="B2" t="n">
-        <v>98135</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,51 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631825</v>
+        <v>631876</v>
       </c>
       <c r="R2" t="n">
-        <v>6899023</v>
+        <v>6898985</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124655288</v>
+        <v>124658193</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>79795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +809,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631978</v>
+        <v>631827</v>
       </c>
       <c r="R3" t="n">
-        <v>6899040</v>
+        <v>6899028</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655624</v>
+        <v>124657989</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,51 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631876</v>
+        <v>631885</v>
       </c>
       <c r="R4" t="n">
-        <v>6898985</v>
+        <v>6899120</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124657511</v>
+        <v>124655748</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>91023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1033,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631929</v>
+        <v>631831</v>
       </c>
       <c r="R5" t="n">
-        <v>6899210</v>
+        <v>6899048</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1284,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658193</v>
+        <v>124657528</v>
       </c>
       <c r="B7" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,38 +1291,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631827</v>
+        <v>631929</v>
       </c>
       <c r="R7" t="n">
-        <v>6899028</v>
+        <v>6899210</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1359,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658065</v>
+        <v>124655288</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,21 +1416,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1436,10 +1440,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631895</v>
+        <v>631978</v>
       </c>
       <c r="R8" t="n">
-        <v>6899098</v>
+        <v>6899040</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124655748</v>
+        <v>124658225</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>98135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,21 +1528,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631831</v>
+        <v>631825</v>
       </c>
       <c r="R9" t="n">
-        <v>6899048</v>
+        <v>6899023</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1583,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124657989</v>
+        <v>124658065</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,25 +1636,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1660,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631885</v>
+        <v>631895</v>
       </c>
       <c r="R10" t="n">
-        <v>6899120</v>
+        <v>6899098</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1695,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124655624</v>
+        <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>95551</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,51 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631876</v>
+        <v>631932</v>
       </c>
       <c r="R2" t="n">
-        <v>6898985</v>
+        <v>6898972</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +785,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -909,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124657989</v>
+        <v>124655597</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>95335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +949,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631885</v>
+        <v>631884</v>
       </c>
       <c r="R4" t="n">
-        <v>6899120</v>
+        <v>6899003</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124655748</v>
+        <v>124658225</v>
       </c>
       <c r="B5" t="n">
-        <v>91023</v>
+        <v>98135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1070,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631831</v>
+        <v>631825</v>
       </c>
       <c r="R5" t="n">
-        <v>6899048</v>
+        <v>6899023</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124659053</v>
+        <v>124655288</v>
       </c>
       <c r="B6" t="n">
-        <v>95551</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,47 +1178,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631932</v>
+        <v>631978</v>
       </c>
       <c r="R6" t="n">
-        <v>6898972</v>
+        <v>6899040</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1251,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,26 +1262,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1400,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124655288</v>
+        <v>124658065</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,21 +1415,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631978</v>
+        <v>631895</v>
       </c>
       <c r="R8" t="n">
-        <v>6899040</v>
+        <v>6899098</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124658225</v>
+        <v>124657989</v>
       </c>
       <c r="B9" t="n">
-        <v>98135</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,34 +1527,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631825</v>
+        <v>631885</v>
       </c>
       <c r="R9" t="n">
-        <v>6899023</v>
+        <v>6899120</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1587,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124658065</v>
+        <v>124655748</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,38 +1635,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631895</v>
+        <v>631831</v>
       </c>
       <c r="R10" t="n">
-        <v>6899098</v>
+        <v>6899048</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1699,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1708,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124655597</v>
+        <v>124655624</v>
       </c>
       <c r="B11" t="n">
-        <v>95335</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,50 +1747,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631884</v>
+        <v>631876</v>
       </c>
       <c r="R11" t="n">
-        <v>6899003</v>
+        <v>6898985</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124659053</v>
+        <v>124657528</v>
       </c>
       <c r="B2" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631932</v>
+        <v>631929</v>
       </c>
       <c r="R2" t="n">
-        <v>6898972</v>
+        <v>6899210</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,26 +780,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -933,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655597</v>
+        <v>124655624</v>
       </c>
       <c r="B4" t="n">
-        <v>95335</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,50 +920,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631884</v>
+        <v>631876</v>
       </c>
       <c r="R4" t="n">
-        <v>6899003</v>
+        <v>6898985</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658225</v>
+        <v>124655597</v>
       </c>
       <c r="B5" t="n">
-        <v>98135</v>
+        <v>95335</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,34 +1046,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631825</v>
+        <v>631884</v>
       </c>
       <c r="R5" t="n">
-        <v>6899023</v>
+        <v>6899003</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1129,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124655288</v>
+        <v>124658065</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1206,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631978</v>
+        <v>631895</v>
       </c>
       <c r="R6" t="n">
-        <v>6899040</v>
+        <v>6899098</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1241,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124657528</v>
+        <v>124657989</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,47 +1275,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631929</v>
+        <v>631885</v>
       </c>
       <c r="R7" t="n">
-        <v>6899210</v>
+        <v>6899120</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1362,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658065</v>
+        <v>124655288</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,21 +1391,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631895</v>
+        <v>631978</v>
       </c>
       <c r="R8" t="n">
-        <v>6899098</v>
+        <v>6899040</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124657989</v>
+        <v>124659053</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>95551</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,34 +1503,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631885</v>
+        <v>631932</v>
       </c>
       <c r="R9" t="n">
-        <v>6899120</v>
+        <v>6898972</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1581,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,6 +1597,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1735,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124655624</v>
+        <v>124658225</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>98135</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,51 +1757,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631876</v>
+        <v>631825</v>
       </c>
       <c r="R11" t="n">
-        <v>6898985</v>
+        <v>6899023</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658193</v>
+        <v>124655624</v>
       </c>
       <c r="B3" t="n">
-        <v>79795</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +808,51 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631827</v>
+        <v>631876</v>
       </c>
       <c r="R3" t="n">
-        <v>6899028</v>
+        <v>6898985</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655624</v>
+        <v>124655597</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>95335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,51 +930,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631876</v>
+        <v>631884</v>
       </c>
       <c r="R4" t="n">
-        <v>6898985</v>
+        <v>6899003</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124655597</v>
+        <v>124658193</v>
       </c>
       <c r="B5" t="n">
-        <v>95335</v>
+        <v>79795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,43 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631884</v>
+        <v>631827</v>
       </c>
       <c r="R5" t="n">
-        <v>6899003</v>
+        <v>6899028</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124657528</v>
+        <v>124658065</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631929</v>
+        <v>631895</v>
       </c>
       <c r="R2" t="n">
-        <v>6899210</v>
+        <v>6899098</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124655624</v>
+        <v>124655288</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,47 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631876</v>
+        <v>631978</v>
       </c>
       <c r="R3" t="n">
-        <v>6898985</v>
+        <v>6899040</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655597</v>
+        <v>124657528</v>
       </c>
       <c r="B4" t="n">
-        <v>95335</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,47 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631884</v>
+        <v>631929</v>
       </c>
       <c r="R4" t="n">
-        <v>6899003</v>
+        <v>6899210</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658193</v>
+        <v>124655624</v>
       </c>
       <c r="B5" t="n">
-        <v>79795</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,41 +1032,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631827</v>
+        <v>631876</v>
       </c>
       <c r="R5" t="n">
-        <v>6899028</v>
+        <v>6898985</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658065</v>
+        <v>124658225</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,38 +1154,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631895</v>
+        <v>631825</v>
       </c>
       <c r="R6" t="n">
-        <v>6899098</v>
+        <v>6899023</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1226,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1375,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124655288</v>
+        <v>124659053</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>95551</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,38 +1378,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631978</v>
+        <v>631932</v>
       </c>
       <c r="R8" t="n">
-        <v>6899040</v>
+        <v>6898972</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,6 +1476,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1487,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124659053</v>
+        <v>124655597</v>
       </c>
       <c r="B9" t="n">
-        <v>95551</v>
+        <v>95335</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1528,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1527,7 +1552,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1536,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631932</v>
+        <v>631884</v>
       </c>
       <c r="R9" t="n">
-        <v>6898972</v>
+        <v>6899003</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1571,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,12 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,26 +1617,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124655748</v>
+        <v>124658193</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>79795</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631831</v>
+        <v>631827</v>
       </c>
       <c r="R10" t="n">
-        <v>6899048</v>
+        <v>6899028</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124658225</v>
+        <v>124655748</v>
       </c>
       <c r="B11" t="n">
-        <v>98135</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631825</v>
+        <v>631831</v>
       </c>
       <c r="R11" t="n">
-        <v>6899023</v>
+        <v>6899048</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658065</v>
+        <v>124658225</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631895</v>
+        <v>631825</v>
       </c>
       <c r="R2" t="n">
-        <v>6899098</v>
+        <v>6899023</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124655288</v>
+        <v>124655624</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631978</v>
+        <v>631876</v>
       </c>
       <c r="R3" t="n">
-        <v>6899040</v>
+        <v>6898985</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124657528</v>
+        <v>124655748</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631929</v>
+        <v>631831</v>
       </c>
       <c r="R4" t="n">
-        <v>6899210</v>
+        <v>6899048</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124655624</v>
+        <v>124659053</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>95551</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,51 +1033,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631876</v>
+        <v>631932</v>
       </c>
       <c r="R5" t="n">
-        <v>6898985</v>
+        <v>6898972</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,6 +1131,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1142,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658225</v>
+        <v>124658065</v>
       </c>
       <c r="B6" t="n">
-        <v>98135</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,38 +1179,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631825</v>
+        <v>631895</v>
       </c>
       <c r="R6" t="n">
-        <v>6899023</v>
+        <v>6899098</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124657989</v>
+        <v>124657528</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,38 +1291,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631885</v>
+        <v>631929</v>
       </c>
       <c r="R7" t="n">
-        <v>6899120</v>
+        <v>6899210</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124659053</v>
+        <v>124658193</v>
       </c>
       <c r="B8" t="n">
-        <v>95551</v>
+        <v>79795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,43 +1416,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631932</v>
+        <v>631827</v>
       </c>
       <c r="R8" t="n">
-        <v>6898972</v>
+        <v>6899028</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,12 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,26 +1496,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124658193</v>
+        <v>124655288</v>
       </c>
       <c r="B10" t="n">
-        <v>79795</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,38 +1645,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631827</v>
+        <v>631978</v>
       </c>
       <c r="R10" t="n">
-        <v>6899028</v>
+        <v>6899040</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124655748</v>
+        <v>124657989</v>
       </c>
       <c r="B11" t="n">
-        <v>91023</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,34 +1761,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631831</v>
+        <v>631885</v>
       </c>
       <c r="R11" t="n">
-        <v>6899048</v>
+        <v>6899120</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658225</v>
+        <v>124658193</v>
       </c>
       <c r="B2" t="n">
-        <v>98135</v>
+        <v>79795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631825</v>
+        <v>631827</v>
       </c>
       <c r="R2" t="n">
-        <v>6899023</v>
+        <v>6899028</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124655624</v>
+        <v>124657528</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,51 +799,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631876</v>
+        <v>631929</v>
       </c>
       <c r="R3" t="n">
-        <v>6898985</v>
+        <v>6899210</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655748</v>
+        <v>124655597</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>95335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +924,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631831</v>
+        <v>631884</v>
       </c>
       <c r="R4" t="n">
-        <v>6899048</v>
+        <v>6899003</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124659053</v>
+        <v>124658225</v>
       </c>
       <c r="B5" t="n">
-        <v>95551</v>
+        <v>98135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,43 +1045,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631932</v>
+        <v>631825</v>
       </c>
       <c r="R5" t="n">
-        <v>6898972</v>
+        <v>6899023</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,26 +1125,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1167,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658065</v>
+        <v>124659053</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>95551</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,38 +1153,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631895</v>
+        <v>631932</v>
       </c>
       <c r="R6" t="n">
-        <v>6899098</v>
+        <v>6898972</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1235,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,6 +1251,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1279,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124657528</v>
+        <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,50 +1299,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631929</v>
+        <v>631876</v>
       </c>
       <c r="R7" t="n">
-        <v>6899210</v>
+        <v>6898985</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1363,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1382,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658193</v>
+        <v>124655288</v>
       </c>
       <c r="B8" t="n">
-        <v>79795</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,38 +1421,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631827</v>
+        <v>631978</v>
       </c>
       <c r="R8" t="n">
-        <v>6899028</v>
+        <v>6899040</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124655597</v>
+        <v>124655748</v>
       </c>
       <c r="B9" t="n">
-        <v>95335</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,43 +1537,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631884</v>
+        <v>631831</v>
       </c>
       <c r="R9" t="n">
-        <v>6899003</v>
+        <v>6899048</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124655288</v>
+        <v>124658065</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631978</v>
+        <v>631895</v>
       </c>
       <c r="R10" t="n">
-        <v>6899040</v>
+        <v>6899098</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658225</v>
+        <v>124655624</v>
       </c>
       <c r="B5" t="n">
-        <v>98135</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,41 +1041,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631825</v>
+        <v>631876</v>
       </c>
       <c r="R5" t="n">
-        <v>6899023</v>
+        <v>6898985</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1287,10 +1297,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124655624</v>
+        <v>124658225</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,51 +1309,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631876</v>
+        <v>631825</v>
       </c>
       <c r="R7" t="n">
-        <v>6898985</v>
+        <v>6899023</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124655624</v>
+        <v>124658225</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>98135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,51 +1041,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631876</v>
+        <v>631825</v>
       </c>
       <c r="R5" t="n">
-        <v>6898985</v>
+        <v>6899023</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1297,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658225</v>
+        <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>98135</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,41 +1299,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631825</v>
+        <v>631876</v>
       </c>
       <c r="R7" t="n">
-        <v>6899023</v>
+        <v>6898985</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658193</v>
+        <v>124655748</v>
       </c>
       <c r="B2" t="n">
-        <v>79795</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631827</v>
+        <v>631831</v>
       </c>
       <c r="R2" t="n">
-        <v>6899028</v>
+        <v>6899048</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124657528</v>
+        <v>124657511</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -820,16 +820,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
@@ -882,6 +873,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655597</v>
+        <v>124658193</v>
       </c>
       <c r="B4" t="n">
-        <v>95335</v>
+        <v>79795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,43 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631884</v>
+        <v>631827</v>
       </c>
       <c r="R4" t="n">
-        <v>6899003</v>
+        <v>6899028</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658225</v>
+        <v>124655597</v>
       </c>
       <c r="B5" t="n">
-        <v>98135</v>
+        <v>95335</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,34 +1032,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631825</v>
+        <v>631884</v>
       </c>
       <c r="R5" t="n">
-        <v>6899023</v>
+        <v>6899003</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124659053</v>
+        <v>124655624</v>
       </c>
       <c r="B6" t="n">
-        <v>95551</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,50 +1149,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631932</v>
+        <v>631876</v>
       </c>
       <c r="R6" t="n">
-        <v>6898972</v>
+        <v>6898985</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,12 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,26 +1243,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1287,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124655624</v>
+        <v>124659053</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>95551</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,51 +1271,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631876</v>
+        <v>631932</v>
       </c>
       <c r="R7" t="n">
-        <v>6898985</v>
+        <v>6898972</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1382,7 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,6 +1369,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1521,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124655748</v>
+        <v>124658225</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>98135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,21 +1533,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1561,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631831</v>
+        <v>631825</v>
       </c>
       <c r="R9" t="n">
-        <v>6899048</v>
+        <v>6899023</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1596,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1606,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124658065</v>
+        <v>124657989</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,25 +1641,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631895</v>
+        <v>631885</v>
       </c>
       <c r="R10" t="n">
-        <v>6899098</v>
+        <v>6899120</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1708,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124657989</v>
+        <v>124658065</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,25 +1753,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631885</v>
+        <v>631895</v>
       </c>
       <c r="R11" t="n">
-        <v>6899120</v>
+        <v>6899098</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124655748</v>
+        <v>124657989</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631831</v>
+        <v>631885</v>
       </c>
       <c r="R2" t="n">
-        <v>6899048</v>
+        <v>6899120</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658193</v>
+        <v>124659053</v>
       </c>
       <c r="B4" t="n">
-        <v>79795</v>
+        <v>95551</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631827</v>
+        <v>631932</v>
       </c>
       <c r="R4" t="n">
-        <v>6899028</v>
+        <v>6898972</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +1014,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124655597</v>
+        <v>124658193</v>
       </c>
       <c r="B5" t="n">
-        <v>95335</v>
+        <v>79795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,43 +1066,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631884</v>
+        <v>631827</v>
       </c>
       <c r="R5" t="n">
-        <v>6899003</v>
+        <v>6899028</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124655624</v>
+        <v>124655748</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,51 +1174,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631876</v>
+        <v>631831</v>
       </c>
       <c r="R6" t="n">
-        <v>6898985</v>
+        <v>6899048</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124659053</v>
+        <v>124658065</v>
       </c>
       <c r="B7" t="n">
-        <v>95551</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,47 +1286,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631932</v>
+        <v>631895</v>
       </c>
       <c r="R7" t="n">
-        <v>6898972</v>
+        <v>6899098</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,26 +1370,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1405,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124655288</v>
+        <v>124655624</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,37 +1402,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631978</v>
+        <v>631876</v>
       </c>
       <c r="R8" t="n">
-        <v>6899040</v>
+        <v>6898985</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124658225</v>
+        <v>124655597</v>
       </c>
       <c r="B9" t="n">
-        <v>98135</v>
+        <v>95335</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,34 +1524,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631825</v>
+        <v>631884</v>
       </c>
       <c r="R9" t="n">
-        <v>6899023</v>
+        <v>6899003</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124657989</v>
+        <v>124655288</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631885</v>
+        <v>631978</v>
       </c>
       <c r="R10" t="n">
-        <v>6899120</v>
+        <v>6899040</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124658065</v>
+        <v>124658225</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98135</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,38 +1753,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631895</v>
+        <v>631825</v>
       </c>
       <c r="R11" t="n">
-        <v>6899098</v>
+        <v>6899023</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124657989</v>
+        <v>124655748</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631885</v>
+        <v>631831</v>
       </c>
       <c r="R2" t="n">
-        <v>6899120</v>
+        <v>6899048</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124657511</v>
+        <v>124655288</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631929</v>
+        <v>631978</v>
       </c>
       <c r="R3" t="n">
-        <v>6899210</v>
+        <v>6899040</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124659053</v>
+        <v>124658193</v>
       </c>
       <c r="B4" t="n">
-        <v>95551</v>
+        <v>79795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,43 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631932</v>
+        <v>631827</v>
       </c>
       <c r="R4" t="n">
-        <v>6898972</v>
+        <v>6899028</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,26 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1050,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658193</v>
+        <v>124658225</v>
       </c>
       <c r="B5" t="n">
-        <v>79795</v>
+        <v>98135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631827</v>
+        <v>631825</v>
       </c>
       <c r="R5" t="n">
-        <v>6899028</v>
+        <v>6899023</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1162,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124655748</v>
+        <v>124658065</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,38 +1135,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631831</v>
+        <v>631895</v>
       </c>
       <c r="R6" t="n">
-        <v>6899048</v>
+        <v>6899098</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1237,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658065</v>
+        <v>124655597</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,38 +1247,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631895</v>
+        <v>631884</v>
       </c>
       <c r="R7" t="n">
-        <v>6899098</v>
+        <v>6899003</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1349,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1508,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124655597</v>
+        <v>124657511</v>
       </c>
       <c r="B9" t="n">
-        <v>95335</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,47 +1490,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631884</v>
+        <v>631929</v>
       </c>
       <c r="R9" t="n">
-        <v>6899003</v>
+        <v>6899210</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1592,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1563,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124655288</v>
+        <v>124659053</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>95551</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,38 +1607,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631978</v>
+        <v>631932</v>
       </c>
       <c r="R10" t="n">
-        <v>6899040</v>
+        <v>6898972</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1689,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,6 +1705,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124658225</v>
+        <v>124657989</v>
       </c>
       <c r="B11" t="n">
-        <v>98135</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,34 +1757,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631825</v>
+        <v>631885</v>
       </c>
       <c r="R11" t="n">
-        <v>6899023</v>
+        <v>6899120</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124655748</v>
+        <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>95551</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631831</v>
+        <v>631932</v>
       </c>
       <c r="R2" t="n">
-        <v>6899048</v>
+        <v>6898972</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +785,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +821,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124655288</v>
+        <v>124658065</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +837,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631978</v>
+        <v>631895</v>
       </c>
       <c r="R3" t="n">
-        <v>6899040</v>
+        <v>6899098</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +906,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658193</v>
+        <v>124655597</v>
       </c>
       <c r="B4" t="n">
-        <v>79795</v>
+        <v>95335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +949,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631827</v>
+        <v>631884</v>
       </c>
       <c r="R4" t="n">
-        <v>6899028</v>
+        <v>6899003</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658225</v>
+        <v>124657528</v>
       </c>
       <c r="B5" t="n">
-        <v>98135</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1066,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631825</v>
+        <v>631929</v>
       </c>
       <c r="R5" t="n">
-        <v>6899023</v>
+        <v>6899210</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658065</v>
+        <v>124658225</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,38 +1187,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631895</v>
+        <v>631825</v>
       </c>
       <c r="R6" t="n">
-        <v>6899098</v>
+        <v>6899023</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1260,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124655597</v>
+        <v>124658193</v>
       </c>
       <c r="B7" t="n">
-        <v>95335</v>
+        <v>79795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,43 +1303,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631884</v>
+        <v>631827</v>
       </c>
       <c r="R7" t="n">
-        <v>6899003</v>
+        <v>6899028</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124655624</v>
+        <v>124655748</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,51 +1411,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631876</v>
+        <v>631831</v>
       </c>
       <c r="R8" t="n">
-        <v>6898985</v>
+        <v>6899048</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124657511</v>
+        <v>124655288</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1523,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631929</v>
+        <v>631978</v>
       </c>
       <c r="R9" t="n">
-        <v>6899210</v>
+        <v>6899040</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1553,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,12 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124659053</v>
+        <v>124655624</v>
       </c>
       <c r="B10" t="n">
-        <v>95551</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,50 +1635,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631932</v>
+        <v>631876</v>
       </c>
       <c r="R10" t="n">
-        <v>6898972</v>
+        <v>6898985</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,12 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,26 +1729,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124659053</v>
+        <v>124655288</v>
       </c>
       <c r="B2" t="n">
-        <v>95551</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631932</v>
+        <v>631978</v>
       </c>
       <c r="R2" t="n">
-        <v>6898972</v>
+        <v>6899040</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,26 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -821,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658065</v>
+        <v>124655748</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,38 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631895</v>
+        <v>631831</v>
       </c>
       <c r="R3" t="n">
-        <v>6899098</v>
+        <v>6899048</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655597</v>
+        <v>124657528</v>
       </c>
       <c r="B4" t="n">
-        <v>95335</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,47 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631884</v>
+        <v>631929</v>
       </c>
       <c r="R4" t="n">
-        <v>6899003</v>
+        <v>6899210</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1017,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124657528</v>
+        <v>124658193</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,47 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631929</v>
+        <v>631827</v>
       </c>
       <c r="R5" t="n">
-        <v>6899210</v>
+        <v>6899028</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1138,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658225</v>
+        <v>124655624</v>
       </c>
       <c r="B6" t="n">
-        <v>98135</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,41 +1144,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631825</v>
+        <v>631876</v>
       </c>
       <c r="R6" t="n">
-        <v>6899023</v>
+        <v>6898985</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658193</v>
+        <v>124655597</v>
       </c>
       <c r="B7" t="n">
-        <v>79795</v>
+        <v>95335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,34 +1270,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631827</v>
+        <v>631884</v>
       </c>
       <c r="R7" t="n">
-        <v>6899028</v>
+        <v>6899003</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1362,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124655748</v>
+        <v>124657989</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>90977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,34 +1391,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631831</v>
+        <v>631885</v>
       </c>
       <c r="R8" t="n">
-        <v>6899048</v>
+        <v>6899120</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124655288</v>
+        <v>124658225</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>98135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,38 +1499,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631978</v>
+        <v>631825</v>
       </c>
       <c r="R9" t="n">
-        <v>6899040</v>
+        <v>6899023</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124655624</v>
+        <v>124658065</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1639,47 +1615,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631876</v>
+        <v>631895</v>
       </c>
       <c r="R10" t="n">
-        <v>6898985</v>
+        <v>6899098</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124657989</v>
+        <v>124659053</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
+        <v>95551</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,34 +1727,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631885</v>
+        <v>631932</v>
       </c>
       <c r="R11" t="n">
-        <v>6899120</v>
+        <v>6898972</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1820,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1805,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,6 +1821,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124655288</v>
+        <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>95551</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631978</v>
+        <v>631932</v>
       </c>
       <c r="R2" t="n">
-        <v>6899040</v>
+        <v>6898972</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +785,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +821,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124655748</v>
+        <v>124655288</v>
       </c>
       <c r="B3" t="n">
-        <v>91023</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +833,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631831</v>
+        <v>631978</v>
       </c>
       <c r="R3" t="n">
-        <v>6899048</v>
+        <v>6899040</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +906,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124657528</v>
+        <v>124655597</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>95335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +945,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631929</v>
+        <v>631884</v>
       </c>
       <c r="R4" t="n">
-        <v>6899210</v>
+        <v>6899003</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1054,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658193</v>
+        <v>124658225</v>
       </c>
       <c r="B5" t="n">
-        <v>79795</v>
+        <v>98135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1070,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631827</v>
+        <v>631825</v>
       </c>
       <c r="R5" t="n">
-        <v>6899028</v>
+        <v>6899023</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1254,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124655597</v>
+        <v>124657989</v>
       </c>
       <c r="B7" t="n">
-        <v>95335</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,43 +1304,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631884</v>
+        <v>631885</v>
       </c>
       <c r="R7" t="n">
-        <v>6899003</v>
+        <v>6899120</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124657989</v>
+        <v>124655748</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,34 +1416,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631885</v>
+        <v>631831</v>
       </c>
       <c r="R8" t="n">
-        <v>6899120</v>
+        <v>6899048</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124658225</v>
+        <v>124658193</v>
       </c>
       <c r="B9" t="n">
-        <v>98135</v>
+        <v>79795</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,21 +1528,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631825</v>
+        <v>631827</v>
       </c>
       <c r="R9" t="n">
-        <v>6899023</v>
+        <v>6899028</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1711,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124659053</v>
+        <v>124657511</v>
       </c>
       <c r="B11" t="n">
-        <v>95551</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,47 +1748,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631932</v>
+        <v>631929</v>
       </c>
       <c r="R11" t="n">
-        <v>6898972</v>
+        <v>6899210</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1795,7 +1811,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,12 +1821,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På murken granstubbe</t>
+          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,26 +1837,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124659053</v>
+        <v>124658193</v>
       </c>
       <c r="B2" t="n">
-        <v>95551</v>
+        <v>79932</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631932</v>
+        <v>631827</v>
       </c>
       <c r="R2" t="n">
-        <v>6898972</v>
+        <v>6899028</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,26 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -821,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124655288</v>
+        <v>124658065</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631978</v>
+        <v>631895</v>
       </c>
       <c r="R3" t="n">
-        <v>6899040</v>
+        <v>6899098</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655597</v>
+        <v>124657528</v>
       </c>
       <c r="B4" t="n">
-        <v>95335</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,47 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631884</v>
+        <v>631929</v>
       </c>
       <c r="R4" t="n">
-        <v>6899003</v>
+        <v>6899210</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1017,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658225</v>
+        <v>124655288</v>
       </c>
       <c r="B5" t="n">
-        <v>98135</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,38 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631825</v>
+        <v>631978</v>
       </c>
       <c r="R5" t="n">
-        <v>6899023</v>
+        <v>6899040</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1129,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124655624</v>
+        <v>124659053</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>95719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,51 +1144,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631876</v>
+        <v>631932</v>
       </c>
       <c r="R6" t="n">
-        <v>6898985</v>
+        <v>6898972</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1251,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1261,7 +1226,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,6 +1242,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1288,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124657989</v>
+        <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>57632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,41 +1290,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631885</v>
+        <v>631876</v>
       </c>
       <c r="R7" t="n">
-        <v>6899120</v>
+        <v>6898985</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124655748</v>
+        <v>124657989</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,34 +1416,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631831</v>
+        <v>631885</v>
       </c>
       <c r="R8" t="n">
-        <v>6899048</v>
+        <v>6899120</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124658193</v>
+        <v>124655748</v>
       </c>
       <c r="B9" t="n">
-        <v>79795</v>
+        <v>91177</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,21 +1528,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631827</v>
+        <v>631831</v>
       </c>
       <c r="R9" t="n">
-        <v>6899028</v>
+        <v>6899048</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124658065</v>
+        <v>124655597</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>95503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,38 +1636,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631895</v>
+        <v>631884</v>
       </c>
       <c r="R10" t="n">
-        <v>6899098</v>
+        <v>6899003</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1699,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124657511</v>
+        <v>124658225</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>98303</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,38 +1757,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631929</v>
+        <v>631825</v>
       </c>
       <c r="R11" t="n">
-        <v>6899210</v>
+        <v>6899023</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1811,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1821,12 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,12 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57681</v>
+        <v>57881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -1281,7 +1281,7 @@
         <v>124655624</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658193</v>
+        <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631827</v>
+        <v>631932</v>
       </c>
       <c r="R2" t="n">
-        <v>6899028</v>
+        <v>6898972</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På murken granstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +780,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,15 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658065</v>
+        <v>124655288</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +827,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631895</v>
+        <v>631978</v>
       </c>
       <c r="R3" t="n">
-        <v>6899098</v>
+        <v>6899040</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,59 +923,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124657528</v>
+        <v>124655748</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631929</v>
+        <v>631831</v>
       </c>
       <c r="R4" t="n">
-        <v>6899210</v>
+        <v>6899048</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,50 +1030,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124655288</v>
+        <v>124655597</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631978</v>
+        <v>631884</v>
       </c>
       <c r="R5" t="n">
-        <v>6899040</v>
+        <v>6899003</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,15 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124659053</v>
+        <v>124657989</v>
       </c>
       <c r="B6" t="n">
-        <v>95719</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,43 +1157,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631932</v>
+        <v>631885</v>
       </c>
       <c r="R6" t="n">
-        <v>6898972</v>
+        <v>6899120</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,12 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På murken granstubbe</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,26 +1237,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1278,58 +1253,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124655624</v>
+        <v>124658065</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631876</v>
+        <v>631895</v>
       </c>
       <c r="R7" t="n">
-        <v>6898985</v>
+        <v>6899098</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,15 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124657989</v>
+        <v>124658193</v>
       </c>
       <c r="B8" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,34 +1371,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631885</v>
+        <v>631827</v>
       </c>
       <c r="R8" t="n">
-        <v>6899120</v>
+        <v>6899028</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,15 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124655748</v>
+        <v>124655624</v>
       </c>
       <c r="B9" t="n">
-        <v>91177</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,37 +1478,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631831</v>
+        <v>631876</v>
       </c>
       <c r="R9" t="n">
-        <v>6899048</v>
+        <v>6898985</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,15 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124655597</v>
+        <v>124658225</v>
       </c>
       <c r="B10" t="n">
-        <v>95503</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,43 +1595,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsikberget, Ännsikberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631884</v>
+        <v>631825</v>
       </c>
       <c r="R10" t="n">
-        <v>6899003</v>
+        <v>6899023</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1703,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,50 +1691,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124658225</v>
+        <v>124657511</v>
       </c>
       <c r="B11" t="n">
-        <v>98303</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsikberget, Ännsikberget, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631825</v>
+        <v>631929</v>
       </c>
       <c r="R11" t="n">
-        <v>6899023</v>
+        <v>6899210</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1815,7 +1761,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1771,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Totalt ca 15-20 bladrosetter spridda inom 2 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -813,6 +818,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124659053</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655288</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655748</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655597</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657989</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,6 +1387,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658065</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658193</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655624</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658225</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1800,8 +1850,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>96554</v>
+        <v>96725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15274-2025 artfynd.xlsx
+++ b/artfynd/A 15274-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>124659053</v>
       </c>
       <c r="B2" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
